--- a/AfterToken/Configs/GameConfig/Datas/unlock.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/unlock.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
     </row>
     <row r="4">
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -552,26 +552,26 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Stage 2: clear Stage 1</t>
+          <t>Stage 102: clear Stage 101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -579,99 +579,45 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Stage 3: clear Stage 2</t>
+          <t>Stage 103: clear Stage 102</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>102</v>
+        <v>1004</v>
       </c>
       <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
-        <v>101</v>
-      </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H6" t="inlineStr">
-        <is>
-          <t>Stage 102: clear Stage 101</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>103</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>102</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Stage 103: clear Stage 102</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1004</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>300</v>
-      </c>
-      <c r="H8" t="inlineStr">
         <is>
           <t>Sniper: player Lv2 + 300G</t>
         </is>
